--- a/合同全生命周期管理系统-项目管理套件/03_需求与范围管理/需求与范围管理-20260918-V7.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/03_需求与范围管理/需求与范围管理-20260918-V7.xlsx
@@ -2223,12 +2223,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>范围总览</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>顶部六项统计为公式联动：需求总数/P0/待确认来自需求池，范围项与包含、排除来自范围基线，追踪覆盖率来自追踪矩阵；灰色计算字段随台账自动更新</t>
         </is>
@@ -15558,37 +15558,37 @@
     <row r="5">
       <c r="A5" s="27">
         <f>COUNTIF(需求池!$A$5:$A$100,"REQ-*")</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="B5" s="51" t="n"/>
       <c r="C5" s="27">
         <f>COUNTIF(需求池!$F$5:$F$100,"P0")</f>
-        <v>19</v>
+        <v/>
       </c>
       <c r="D5" s="51" t="n"/>
       <c r="E5" s="27">
         <f>COUNTIF(需求池!$I$5:$I$100,"待*")</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="F5" s="51" t="n"/>
       <c r="G5" s="27">
         <f>COUNTIF(范围基线!$A$5:$A$100,"SCP-*")</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="H5" s="51" t="n"/>
       <c r="I5" s="27">
         <f>COUNTIF(范围基线!$D$5:$D$100,"包含")+COUNTIF(范围基线!$D$5:$D$100,"条件包含")</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="J5" s="51" t="n"/>
       <c r="K5" s="27">
         <f>COUNTIF(范围基线!$D$5:$D$100,"不包含")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="L5" s="51" t="n"/>
       <c r="M5" s="52">
         <f>IF(COUNTIF(需求追踪矩阵!$C$5:$C$100,"P0")=0,0,COUNTIFS(需求追踪矩阵!$C$5:$C$100,"P0",需求追踪矩阵!$N$5:$N$100,"完整")/COUNTIF(需求追踪矩阵!$C$5:$C$100,"P0"))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N5" s="51" t="n"/>
     </row>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>测试人员</t>
+          <t>高级测试人员、中级测试人员</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -18601,9 +18601,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N5" s="21" t="str">
+      <c r="N5" s="21">
         <f>IF($C5&lt;&gt;"P0","按需",IF(COUNTBLANK($E5:$J5)+COUNTIF($E5:$J5,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -18672,9 +18672,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N6" s="21" t="str">
+      <c r="N6" s="21">
         <f>IF($C6&lt;&gt;"P0","按需",IF(COUNTBLANK($E6:$J6)+COUNTIF($E6:$J6,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -18743,9 +18743,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N7" s="21" t="str">
+      <c r="N7" s="21">
         <f>IF($C7&lt;&gt;"P0","按需",IF(COUNTBLANK($E7:$J7)+COUNTIF($E7:$J7,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -18814,9 +18814,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N8" s="21" t="str">
+      <c r="N8" s="21">
         <f>IF($C8&lt;&gt;"P0","按需",IF(COUNTBLANK($E8:$J8)+COUNTIF($E8:$J8,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -18885,9 +18885,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N9" s="21" t="str">
+      <c r="N9" s="21">
         <f>IF($C9&lt;&gt;"P0","按需",IF(COUNTBLANK($E9:$J9)+COUNTIF($E9:$J9,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -18956,9 +18956,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N10" s="21" t="str">
+      <c r="N10" s="21">
         <f>IF($C10&lt;&gt;"P0","按需",IF(COUNTBLANK($E10:$J10)+COUNTIF($E10:$J10,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -19027,9 +19027,9 @@
           <t>待验证</t>
         </is>
       </c>
-      <c r="N11" s="21" t="str">
+      <c r="N11" s="21">
         <f>IF($C11&lt;&gt;"P0","按需",IF(COUNTBLANK($E11:$J11)+COUNTIF($E11:$J11,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -19098,9 +19098,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N12" s="21" t="str">
+      <c r="N12" s="21">
         <f>IF($C12&lt;&gt;"P0","按需",IF(COUNTBLANK($E12:$J12)+COUNTIF($E12:$J12,"待补充")=0,"完整","不完整"))</f>
-        <v>按需</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -19169,9 +19169,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N13" s="21" t="str">
+      <c r="N13" s="21">
         <f>IF($C13&lt;&gt;"P0","按需",IF(COUNTBLANK($E13:$J13)+COUNTIF($E13:$J13,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -19240,9 +19240,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N14" s="21" t="str">
+      <c r="N14" s="21">
         <f>IF($C14&lt;&gt;"P0","按需",IF(COUNTBLANK($E14:$J14)+COUNTIF($E14:$J14,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -19311,9 +19311,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N15" s="21" t="str">
+      <c r="N15" s="21">
         <f>IF($C15&lt;&gt;"P0","按需",IF(COUNTBLANK($E15:$J15)+COUNTIF($E15:$J15,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -19382,9 +19382,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N16" s="21" t="str">
+      <c r="N16" s="21">
         <f>IF($C16&lt;&gt;"P0","按需",IF(COUNTBLANK($E16:$J16)+COUNTIF($E16:$J16,"待补充")=0,"完整","不完整"))</f>
-        <v>按需</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -19453,9 +19453,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N17" s="21" t="str">
+      <c r="N17" s="21">
         <f>IF($C17&lt;&gt;"P0","按需",IF(COUNTBLANK($E17:$J17)+COUNTIF($E17:$J17,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -19524,9 +19524,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N18" s="21" t="str">
+      <c r="N18" s="21">
         <f>IF($C18&lt;&gt;"P0","按需",IF(COUNTBLANK($E18:$J18)+COUNTIF($E18:$J18,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -19595,9 +19595,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N19" s="21" t="str">
+      <c r="N19" s="21">
         <f>IF($C19&lt;&gt;"P0","按需",IF(COUNTBLANK($E19:$J19)+COUNTIF($E19:$J19,"待补充")=0,"完整","不完整"))</f>
-        <v>按需</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -19666,9 +19666,9 @@
           <t>待验证</t>
         </is>
       </c>
-      <c r="N20" s="21" t="str">
+      <c r="N20" s="21">
         <f>IF($C20&lt;&gt;"P0","按需",IF(COUNTBLANK($E20:$J20)+COUNTIF($E20:$J20,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -19737,9 +19737,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N21" s="21" t="str">
+      <c r="N21" s="21">
         <f>IF($C21&lt;&gt;"P0","按需",IF(COUNTBLANK($E21:$J21)+COUNTIF($E21:$J21,"待补充")=0,"完整","不完整"))</f>
-        <v>按需</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -19808,9 +19808,9 @@
           <t>待验证</t>
         </is>
       </c>
-      <c r="N22" s="21" t="str">
+      <c r="N22" s="21">
         <f>IF($C22&lt;&gt;"P0","按需",IF(COUNTBLANK($E22:$J22)+COUNTIF($E22:$J22,"待补充")=0,"完整","不完整"))</f>
-        <v>按需</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -19879,9 +19879,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N23" s="21" t="str">
+      <c r="N23" s="21">
         <f>IF($C23&lt;&gt;"P0","按需",IF(COUNTBLANK($E23:$J23)+COUNTIF($E23:$J23,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -19950,9 +19950,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N24" s="21" t="str">
+      <c r="N24" s="21">
         <f>IF($C24&lt;&gt;"P0","按需",IF(COUNTBLANK($E24:$J24)+COUNTIF($E24:$J24,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -20021,9 +20021,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N25" s="21" t="str">
+      <c r="N25" s="21">
         <f>IF($C25&lt;&gt;"P0","按需",IF(COUNTBLANK($E25:$J25)+COUNTIF($E25:$J25,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -20092,9 +20092,9 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="N26" s="21" t="str">
+      <c r="N26" s="21">
         <f>IF($C26&lt;&gt;"P0","按需",IF(COUNTBLANK($E26:$J26)+COUNTIF($E26:$J26,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -20163,9 +20163,9 @@
           <t>待量化</t>
         </is>
       </c>
-      <c r="N27" s="21" t="str">
+      <c r="N27" s="21">
         <f>IF($C27&lt;&gt;"P0","按需",IF(COUNTBLANK($E27:$J27)+COUNTIF($E27:$J27,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -20234,9 +20234,9 @@
           <t>待量化</t>
         </is>
       </c>
-      <c r="N28" s="21" t="str">
+      <c r="N28" s="21">
         <f>IF($C28&lt;&gt;"P0","按需",IF(COUNTBLANK($E28:$J28)+COUNTIF($E28:$J28,"待补充")=0,"完整","不完整"))</f>
-        <v>不完整</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -21641,7 +21641,7 @@
       </c>
       <c r="B7" s="12">
         <f>范围总览!A5</f>
-        <v>24</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -21652,7 +21652,7 @@
       </c>
       <c r="B8" s="12">
         <f>范围总览!C5</f>
-        <v>19</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -21663,7 +21663,7 @@
       </c>
       <c r="B9" s="12">
         <f>范围总览!G5</f>
-        <v>12</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="B10" s="12">
         <f>COUNTIF(WBS字典!$A$5:$A$100,"SCP-WP-*")</f>
-        <v>15</v>
+        <v/>
       </c>
     </row>
     <row r="11">
